--- a/Result/profitability/2399.xlsx
+++ b/Result/profitability/2399.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AM74"/>
+  <dimension ref="A1:AM75"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -669,13 +669,13 @@
         <v>0.3</v>
       </c>
       <c r="M2" t="n">
-        <v>0.215</v>
+        <v>0.49125</v>
       </c>
       <c r="N2" t="n">
-        <v>9.018750000000001</v>
+        <v>8.92375</v>
       </c>
       <c r="O2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P2" t="n">
         <v>1</v>
@@ -687,7 +687,7 @@
         <v>0</v>
       </c>
       <c r="S2" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T2" t="n">
         <v>0</v>
@@ -780,10 +780,10 @@
         <v>0.07000000000000001</v>
       </c>
       <c r="M3" t="n">
-        <v>0.24125</v>
+        <v>0.5075</v>
       </c>
       <c r="N3" t="n">
-        <v>8.952500000000001</v>
+        <v>9.32</v>
       </c>
       <c r="O3" t="n">
         <v>0</v>
@@ -899,13 +899,13 @@
         <v>0.44</v>
       </c>
       <c r="M4" t="n">
-        <v>0.30375</v>
+        <v>0.5549999999999999</v>
       </c>
       <c r="N4" t="n">
-        <v>9.315000000000001</v>
+        <v>9.635</v>
       </c>
       <c r="O4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P4" t="n">
         <v>1</v>
@@ -917,7 +917,7 @@
         <v>0</v>
       </c>
       <c r="S4" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T4" t="n">
         <v>0</v>
@@ -1018,10 +1018,10 @@
         <v>0.29</v>
       </c>
       <c r="M5" t="n">
-        <v>0.3325</v>
+        <v>0.6337499999999999</v>
       </c>
       <c r="N5" t="n">
-        <v>9.731249999999999</v>
+        <v>10.56125</v>
       </c>
       <c r="O5" t="n">
         <v>0</v>
@@ -1042,7 +1042,7 @@
         <v>0</v>
       </c>
       <c r="U5" t="n">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V5" t="n">
         <v>97.40000000000001</v>
@@ -1137,10 +1137,10 @@
         <v>0.88</v>
       </c>
       <c r="M6" t="n">
-        <v>0.485</v>
+        <v>0.7224999999999999</v>
       </c>
       <c r="N6" t="n">
-        <v>11.24625</v>
+        <v>11.71375</v>
       </c>
       <c r="O6" t="n">
         <v>1</v>
@@ -1264,13 +1264,13 @@
         <v>0.49</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5249999999999999</v>
+        <v>0.7524999999999999</v>
       </c>
       <c r="N7" t="n">
-        <v>12.195</v>
+        <v>12.42875</v>
       </c>
       <c r="O7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="P7" t="n">
         <v>1</v>
@@ -1282,7 +1282,7 @@
         <v>0</v>
       </c>
       <c r="S7" t="n">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="T7" t="n">
         <v>0</v>
@@ -1391,10 +1391,10 @@
         <v>0.66</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5762499999999999</v>
+        <v>0.6499999999999999</v>
       </c>
       <c r="N8" t="n">
-        <v>12.85</v>
+        <v>12.075</v>
       </c>
       <c r="O8" t="n">
         <v>1</v>
@@ -2026,7 +2026,7 @@
         <v>-0.13</v>
       </c>
       <c r="M13" t="n">
-        <v>0.4737499999999999</v>
+        <v>0.47375</v>
       </c>
       <c r="N13" t="n">
         <v>13.60375</v>
@@ -9826,6 +9826,133 @@
       </c>
       <c r="AM74" t="n">
         <v>115.1</v>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>2399</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>115.2Q</t>
+        </is>
+      </c>
+      <c r="C75" t="n">
+        <v>529</v>
+      </c>
+      <c r="D75" t="n">
+        <v>474</v>
+      </c>
+      <c r="E75" t="n">
+        <v>54</v>
+      </c>
+      <c r="F75" t="n">
+        <v>10.27</v>
+      </c>
+      <c r="G75" t="n">
+        <v>-80</v>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>-15.08%</t>
+        </is>
+      </c>
+      <c r="I75" t="n">
+        <v>502</v>
+      </c>
+      <c r="J75" t="n">
+        <v>423</v>
+      </c>
+      <c r="K75" t="n">
+        <v>368</v>
+      </c>
+      <c r="L75" t="n">
+        <v>2.07</v>
+      </c>
+      <c r="M75" t="n">
+        <v>0.4362499999999999</v>
+      </c>
+      <c r="N75" t="n">
+        <v>8.921250000000001</v>
+      </c>
+      <c r="O75" t="n">
+        <v>1</v>
+      </c>
+      <c r="P75" t="n">
+        <v>1</v>
+      </c>
+      <c r="Q75" t="n">
+        <v>1</v>
+      </c>
+      <c r="R75" t="n">
+        <v>0</v>
+      </c>
+      <c r="S75" t="n">
+        <v>1</v>
+      </c>
+      <c r="T75" t="n">
+        <v>0</v>
+      </c>
+      <c r="U75" t="n">
+        <v>0</v>
+      </c>
+      <c r="V75" t="n">
+        <v>115.2</v>
+      </c>
+      <c r="W75" t="n">
+        <v>0.5899999999999999</v>
+      </c>
+      <c r="X75" t="n">
+        <v>0.3986486486486485</v>
+      </c>
+      <c r="Y75" t="n">
+        <v>-6.199999999999999</v>
+      </c>
+      <c r="Z75" t="n">
+        <v>-0.3764420157862781</v>
+      </c>
+      <c r="AA75" t="n">
+        <v>2.41</v>
+      </c>
+      <c r="AB75" t="n">
+        <v>-7.088235294117646</v>
+      </c>
+      <c r="AC75" t="n">
+        <v>6.64</v>
+      </c>
+      <c r="AD75" t="n">
+        <v>1.829201101928374</v>
+      </c>
+      <c r="AE75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AF75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AG75" t="n">
+        <v>0</v>
+      </c>
+      <c r="AH75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AI75" t="n">
+        <v>1</v>
+      </c>
+      <c r="AJ75" t="inlineStr">
+        <is>
+          <t>EPS成長 / 毛利率成長</t>
+        </is>
+      </c>
+      <c r="AK75" t="n">
+        <v>115</v>
+      </c>
+      <c r="AL75" t="n">
+        <v>2</v>
+      </c>
+      <c r="AM75" t="n">
+        <v>115.2</v>
       </c>
     </row>
   </sheetData>
